--- a/data/controles_results/dif_medias/controls_staggered_vars/difmedias_controles_staggered_variables_2023_T2_0.xlsx
+++ b/data/controles_results/dif_medias/controls_staggered_vars/difmedias_controles_staggered_variables_2023_T2_0.xlsx
@@ -45,7 +45,7 @@
     <t>N</t>
   </si>
   <si>
-    <t>51</t>
+    <t>45</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -63,28 +63,28 @@
     <t>(0.000)</t>
   </si>
   <si>
-    <t>0.471</t>
-  </si>
-  <si>
-    <t>(0.071)</t>
-  </si>
-  <si>
-    <t>0.353</t>
-  </si>
-  <si>
-    <t>(0.068)</t>
-  </si>
-  <si>
-    <t>1.020</t>
-  </si>
-  <si>
-    <t>(0.203)</t>
-  </si>
-  <si>
-    <t>0.627</t>
-  </si>
-  <si>
-    <t>(0.166)</t>
+    <t>0.533</t>
+  </si>
+  <si>
+    <t>(0.075)</t>
+  </si>
+  <si>
+    <t>0.400</t>
+  </si>
+  <si>
+    <t>(0.074)</t>
+  </si>
+  <si>
+    <t>1.156</t>
+  </si>
+  <si>
+    <t>(0.222)</t>
+  </si>
+  <si>
+    <t>0.711</t>
+  </si>
+  <si>
+    <t>(0.184)</t>
   </si>
   <si>
     <t>65</t>
@@ -123,7 +123,7 @@
     <t>.n</t>
   </si>
   <si>
-    <t>116</t>
+    <t>110</t>
   </si>
   <si>
     <t>(2)-(1)</t>
@@ -135,16 +135,16 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>0.406***</t>
-  </si>
-  <si>
-    <t>0.309***</t>
-  </si>
-  <si>
-    <t>3.319***</t>
-  </si>
-  <si>
-    <t>1.157***</t>
+    <t>0.344***</t>
+  </si>
+  <si>
+    <t>0.262***</t>
+  </si>
+  <si>
+    <t>3.183***</t>
+  </si>
+  <si>
+    <t>1.074***</t>
   </si>
 </sst>
 </file>
